--- a/docs/reports/mkt_roy_add_2026-08-16.xlsx
+++ b/docs/reports/mkt_roy_add_2026-08-16.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="За неделю" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ядро (3 мес)'!$A$1:$H$37</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'За неделю'!$A$1:$L$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Ядро (3 мес)'!$A$1:$H$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'За неделю'!$A$1:$L$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H37"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -480,226 +480,226 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>200166303</v>
+        <v>216421567</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>02807</t>
+          <t>00024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Картридж для Samsung ML-1860</t>
+          <t>Картридж для HP LaserJet 1018</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>95</v>
       </c>
       <c r="F2" t="n">
-        <v>65322</v>
+        <v>96606</v>
       </c>
       <c r="G2" t="n">
-        <v>35.1</v>
+        <v>34.7</v>
       </c>
       <c r="H2" t="n">
-        <v>507</v>
+        <v>720</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>200166274</v>
+        <v>200166303</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>02801</t>
+          <t>02807</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Картридж для Samsung ML-1660</t>
+          <t>Картридж для Samsung ML-1860</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="F3" t="n">
-        <v>30128</v>
+        <v>65322</v>
       </c>
       <c r="G3" t="n">
-        <v>34.9</v>
+        <v>35.1</v>
       </c>
       <c r="H3" t="n">
-        <v>229</v>
+        <v>507</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>199565917</v>
+        <v>200166274</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02792</t>
+          <t>02801</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Картридж для Samsung SCX-4833FD</t>
+          <t>Картридж для Samsung ML-1660</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F4" t="n">
-        <v>22021</v>
+        <v>30128</v>
       </c>
       <c r="G4" t="n">
-        <v>34.6</v>
+        <v>34.9</v>
       </c>
       <c r="H4" t="n">
-        <v>162</v>
+        <v>229</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>192567652</v>
+        <v>199565917</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0720</t>
+          <t>02792</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Картриджи CLT-409 для Samsung CLP-310, CLP-315, CLX-3170</t>
+          <t>Картридж для Samsung SCX-4833FD</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>21976</v>
+        <v>22021</v>
       </c>
       <c r="G5" t="n">
-        <v>51.3</v>
+        <v>34.6</v>
       </c>
       <c r="H5" t="n">
-        <v>445</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>199566477</v>
+        <v>192567652</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>0720</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Картридж для Kyocera EcoSys M2235dn</t>
+          <t>Картриджи CLT-409 для Samsung CLP-310, CLP-315, CLX-3170</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F6" t="n">
-        <v>21924</v>
+        <v>21976</v>
       </c>
       <c r="G6" t="n">
-        <v>29.3</v>
+        <v>51.3</v>
       </c>
       <c r="H6" t="n">
-        <v>72</v>
+        <v>445</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>199573317</v>
+        <v>199566477</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>23191</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Картридж для Lexmark MX317dn</t>
+          <t>Картридж для Kyocera EcoSys M2235dn</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F7" t="n">
-        <v>18752</v>
+        <v>21924</v>
       </c>
       <c r="G7" t="n">
-        <v>30.8</v>
+        <v>29.3</v>
       </c>
       <c r="H7" t="n">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>493592815</v>
+        <v>199573317</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6384</t>
+          <t>23191</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Картридж TL-R5220X для BM5201ADN, BM5201ADW черный</t>
+          <t>Картридж для Lexmark MX317dn</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>18313</v>
+        <v>18752</v>
       </c>
       <c r="G8" t="n">
-        <v>33.7</v>
+        <v>30.8</v>
       </c>
       <c r="H8" t="n">
-        <v>123</v>
+        <v>83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>209731248</v>
+        <v>493592815</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4266</t>
+          <t>6384</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Картридж 006R01703 для Xerox C8045, C8045 пурпурный</t>
+          <t>Картридж TL-R5220X для BM5201ADN, BM5201ADW черный</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -709,87 +709,87 @@
         <v>4</v>
       </c>
       <c r="F9" t="n">
-        <v>17125</v>
+        <v>18313</v>
       </c>
       <c r="G9" t="n">
-        <v>36.9</v>
+        <v>33.7</v>
       </c>
       <c r="H9" t="n">
-        <v>157</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>209779249</v>
+        <v>209731248</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>43662</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Картридж для HP DJ Ink Advantage 2520hc</t>
+          <t>Картридж 006R01703 для Xerox C8045, C8045 пурпурный</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F10" t="n">
-        <v>15571</v>
+        <v>17125</v>
       </c>
       <c r="G10" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="H10" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>262192027</v>
+        <v>209779249</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>43662</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Картридж ML-2010 для Samsung ML-1610, ML-1615 черный</t>
+          <t>Картридж для HP DJ Ink Advantage 2520hc</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>12070</v>
+        <v>15571</v>
       </c>
       <c r="G11" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="H11" t="n">
-        <v>113</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>199335608</v>
+        <v>262192027</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Картридж SCX-4100 для Samsung SCX-4100 черный</t>
+          <t>Картридж ML-2010 для Samsung ML-1610, ML-1615 черный</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -799,477 +799,477 @@
         <v>7</v>
       </c>
       <c r="F12" t="n">
-        <v>11988</v>
+        <v>12070</v>
       </c>
       <c r="G12" t="n">
-        <v>26.4</v>
+        <v>37.1</v>
       </c>
       <c r="H12" t="n">
-        <v>13</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>200166518</v>
+        <v>199335608</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>07822</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Картридж для Kyocera FS-1125MFP</t>
+          <t>Картридж SCX-4100 для Samsung SCX-4100 черный</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F13" t="n">
-        <v>11102</v>
+        <v>11988</v>
       </c>
       <c r="G13" t="n">
-        <v>36.7</v>
+        <v>26.4</v>
       </c>
       <c r="H13" t="n">
-        <v>100</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>262191959</v>
+        <v>200166518</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5482</t>
+          <t>07822</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Картридж TK-1248 для Kyocera MA2001, MA2001W, PA2001 черный</t>
+          <t>Картридж для Kyocera FS-1125MFP</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F14" t="n">
-        <v>10570</v>
+        <v>11102</v>
       </c>
       <c r="G14" t="n">
-        <v>38.9</v>
+        <v>36.8</v>
       </c>
       <c r="H14" t="n">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>216354469</v>
+        <v>262191959</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1189</t>
+          <t>5482</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Фотобарабан CE314A для HP LJ Pro 100 M175a черный</t>
+          <t>Картридж TK-1248 для Kyocera MA2001, MA2001W, PA2001 черный</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>10452</v>
+        <v>10570</v>
       </c>
       <c r="G15" t="n">
-        <v>25.9</v>
+        <v>38.9</v>
       </c>
       <c r="H15" t="n">
-        <v>7</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>199331154</v>
+        <v>216354469</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Картридж ML-1210 для Samsung ML-1010, ML-1020 черный</t>
+          <t>Фотобарабан CE314A для HP LJ Pro 100 M175a черный</t>
         </is>
       </c>
       <c r="D16" t="n">
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F16" t="n">
-        <v>10366</v>
+        <v>10452</v>
       </c>
       <c r="G16" t="n">
-        <v>33.8</v>
+        <v>25.9</v>
       </c>
       <c r="H16" t="n">
-        <v>70</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>209663303</v>
+        <v>199331154</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>02751</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Картридж для Samsung SCX-4600</t>
+          <t>Картридж ML-1210 для Samsung ML-1010, ML-1020 черный</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
-        <v>10138</v>
+        <v>10366</v>
       </c>
       <c r="G17" t="n">
-        <v>35</v>
+        <v>33.8</v>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>199566476</v>
+        <v>209663303</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23655</t>
+          <t>02751</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Картридж для Kyocera EcoSys M2735dn</t>
+          <t>Картридж для Samsung SCX-4600</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F18" t="n">
-        <v>9714</v>
+        <v>10138</v>
       </c>
       <c r="G18" t="n">
-        <v>31.1</v>
+        <v>35</v>
       </c>
       <c r="H18" t="n">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>262192104</v>
+        <v>199566476</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4768</t>
+          <t>23655</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Картридж M21-375595WT для Brady BMP 21-LAB, BMP 21-PLUS</t>
+          <t>Картридж для Kyocera EcoSys M2735dn</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>9170</v>
+        <v>9714</v>
       </c>
       <c r="G19" t="n">
-        <v>55</v>
+        <v>31.1</v>
       </c>
       <c r="H19" t="n">
-        <v>212</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1002610265</v>
+        <v>262192104</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11573</t>
+          <t>4768</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Картридж для HP LaserJet M1536dnf MFP</t>
+          <t>Картридж M21-375595WT для Brady BMP 21-LAB, BMP 21-PLUS</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>2</v>
       </c>
       <c r="E20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F20" t="n">
-        <v>9017</v>
+        <v>9170</v>
       </c>
       <c r="G20" t="n">
-        <v>28.1</v>
+        <v>55</v>
       </c>
       <c r="H20" t="n">
-        <v>22</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>216360999</v>
+        <v>1002610265</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>11573</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Картридж TL-420Е для M6700D, M6700DW, M6800FDW черный</t>
+          <t>Картридж для HP LaserJet M1536dnf MFP</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F21" t="n">
-        <v>8636</v>
+        <v>9017</v>
       </c>
       <c r="G21" t="n">
-        <v>38.1</v>
+        <v>28.1</v>
       </c>
       <c r="H21" t="n">
-        <v>87</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>416649238</v>
+        <v>216360999</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>4821</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Фотобарабан + картридж TN-1075+DR-1075 для Brother черный</t>
+          <t>Картридж TL-420Е для M6700D, M6700DW, M6800FDW черный</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>2</v>
       </c>
       <c r="E22" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F22" t="n">
-        <v>8584</v>
+        <v>8636</v>
       </c>
       <c r="G22" t="n">
-        <v>36.7</v>
+        <v>38.1</v>
       </c>
       <c r="H22" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>200166560</v>
+        <v>416649238</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17182</t>
+          <t>6102</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Картридж для Kyocera EcoSys M2635dn</t>
+          <t>Фотобарабан + картридж TN-1075+DR-1075 для Brother черный</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
-        <v>8565</v>
+        <v>8584</v>
       </c>
       <c r="G23" t="n">
-        <v>30.9</v>
+        <v>36.8</v>
       </c>
       <c r="H23" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>199574658</v>
+        <v>200166560</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>53517</t>
+          <t>17182</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Картридж для Canon i-SENSYS MF3010</t>
+          <t>Картридж для Kyocera EcoSys M2635dn</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>7705</v>
+        <v>8565</v>
       </c>
       <c r="G24" t="n">
-        <v>25.5</v>
+        <v>30.9</v>
       </c>
       <c r="H24" t="n">
-        <v>3</v>
+        <v>39</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>439974378</v>
+        <v>199574658</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>53517</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Картридж 903XL для HP OfficeJet 6950, OfficeJet 6950 черный</t>
+          <t>Картридж для Canon i-SENSYS MF3010</t>
         </is>
       </c>
       <c r="D25" t="n">
         <v>2</v>
       </c>
       <c r="E25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F25" t="n">
-        <v>7627</v>
+        <v>7705</v>
       </c>
       <c r="G25" t="n">
-        <v>41.5</v>
+        <v>25.5</v>
       </c>
       <c r="H25" t="n">
-        <v>97</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>199570371</v>
+        <v>439974378</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>02471</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Картридж для Brother HL-2035R</t>
+          <t>Картридж 903XL для HP OfficeJet 6950, OfficeJet 6950 черный</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F26" t="n">
-        <v>7188</v>
+        <v>7627</v>
       </c>
       <c r="G26" t="n">
-        <v>27.7</v>
+        <v>40.4</v>
       </c>
       <c r="H26" t="n">
-        <v>15</v>
+        <v>90</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>216429080</v>
+        <v>199570371</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>00041</t>
+          <t>02471</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Картридж для HP LaserJet 1300</t>
+          <t>Картридж для Brother HL-2035R</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F27" t="n">
-        <v>6988</v>
+        <v>7188</v>
       </c>
       <c r="G27" t="n">
-        <v>36.2</v>
+        <v>27.7</v>
       </c>
       <c r="H27" t="n">
-        <v>60</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>199572665</v>
+        <v>216429080</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>00041</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Картридж для Ricoh Aficio SP311SFN</t>
+          <t>Картридж для HP LaserJet 1300</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1279,87 +1279,87 @@
         <v>4</v>
       </c>
       <c r="F28" t="n">
-        <v>6531</v>
+        <v>6988</v>
       </c>
       <c r="G28" t="n">
-        <v>34.5</v>
+        <v>36.2</v>
       </c>
       <c r="H28" t="n">
-        <v>48</v>
+        <v>60</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>349940282</v>
+        <v>216422271</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5877</t>
+          <t>000211</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Картридж TN-2590XL для Brother DCP-L2600D, HL-L2402D черный</t>
+          <t>Картридж для HP LaserJet 3050</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="F29" t="n">
-        <v>6089</v>
+        <v>6679</v>
       </c>
       <c r="G29" t="n">
-        <v>25.4</v>
+        <v>34.2</v>
       </c>
       <c r="H29" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>209752248</v>
+        <v>199572665</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Картридж TK-1170XL для Kyocera M2040, M2540, M2540dw черный</t>
+          <t>Картридж для Ricoh Aficio SP311SFN</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>4</v>
       </c>
       <c r="F30" t="n">
-        <v>5802</v>
+        <v>6531</v>
       </c>
       <c r="G30" t="n">
-        <v>32.2</v>
+        <v>34.5</v>
       </c>
       <c r="H30" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>181116389</v>
+        <v>349940282</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2167</t>
+          <t>5877</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Картридж TK-5220BK для Kyocera M5521cdn, M5521cdn черный</t>
+          <t>Картридж TN-2590XL для Brother DCP-L2600D, HL-L2402D черный</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1369,10 +1369,10 @@
         <v>3</v>
       </c>
       <c r="F31" t="n">
-        <v>4788</v>
+        <v>6089</v>
       </c>
       <c r="G31" t="n">
-        <v>25.5</v>
+        <v>25.4</v>
       </c>
       <c r="H31" t="n">
         <v>2</v>
@@ -1380,46 +1380,46 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>216354204</v>
+        <v>209752248</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1169</t>
+          <t>5248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Фотобарабан 101R00474 DU для Xerox Phaser 3052 черный</t>
+          <t>Картридж TK-1170XL для Kyocera M2040, M2540, M2540dw черный</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F32" t="n">
-        <v>4229</v>
+        <v>5802</v>
       </c>
       <c r="G32" t="n">
-        <v>26.5</v>
+        <v>32.2</v>
       </c>
       <c r="H32" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>200167538</v>
+        <v>181116389</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>32629</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Картридж для P2500W</t>
+          <t>Картридж TK-5220BK для Kyocera M5521cdn, M5521cdn черный</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1429,57 +1429,57 @@
         <v>3</v>
       </c>
       <c r="F33" t="n">
-        <v>4149</v>
+        <v>4788</v>
       </c>
       <c r="G33" t="n">
-        <v>35.5</v>
+        <v>25.5</v>
       </c>
       <c r="H33" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>181120378</v>
+        <v>216354204</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>4411</t>
+          <t>1169</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Картриджи CLI-426 для Canon Pixma MG6240, Pixma MG6240</t>
+          <t>Фотобарабан 101R00474 DU для Xerox Phaser 3052 черный</t>
         </is>
       </c>
       <c r="D34" t="n">
         <v>2</v>
       </c>
       <c r="E34" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F34" t="n">
-        <v>3853</v>
+        <v>4229</v>
       </c>
       <c r="G34" t="n">
-        <v>44.5</v>
+        <v>26.5</v>
       </c>
       <c r="H34" t="n">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>199566489</v>
+        <v>200167538</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>07811</t>
+          <t>32629</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Картридж для Kyocera FS-1040</t>
+          <t>Картридж для P2500W</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1489,77 +1489,137 @@
         <v>3</v>
       </c>
       <c r="F35" t="n">
-        <v>3356</v>
+        <v>4149</v>
       </c>
       <c r="G35" t="n">
-        <v>31.8</v>
+        <v>35.5</v>
       </c>
       <c r="H35" t="n">
-        <v>18</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>181097446</v>
+        <v>181120378</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0904</t>
+          <t>4411</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Картридж LC-1240Y для Brother MFC-J6510DW желтый</t>
+          <t>Картриджи CLI-426 для Canon Pixma MG6240, Pixma MG6240</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F36" t="n">
-        <v>2483</v>
+        <v>3853</v>
       </c>
       <c r="G36" t="n">
-        <v>40.8</v>
+        <v>44.5</v>
       </c>
       <c r="H36" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
+        <v>199566489</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>07811</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Картридж для Kyocera FS-1040</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>2</v>
+      </c>
+      <c r="E37" t="n">
+        <v>3</v>
+      </c>
+      <c r="F37" t="n">
+        <v>3356</v>
+      </c>
+      <c r="G37" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="H37" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>181097446</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0904</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Картридж LC-1240Y для Brother MFC-J6510DW желтый</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" t="n">
+        <v>2483</v>
+      </c>
+      <c r="G38" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
         <v>200163032</v>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>14451</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Картридж для Canon Pixma mini 260</t>
         </is>
       </c>
-      <c r="D37" t="n">
-        <v>2</v>
-      </c>
-      <c r="E37" t="n">
-        <v>3</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="D39" t="n">
+        <v>2</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3</v>
+      </c>
+      <c r="F39" t="n">
         <v>1902</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G39" t="n">
         <v>43.1</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H39" t="n">
         <v>27</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H37"/>
+  <autoFilter ref="A1:H39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1570,7 +1630,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1748,10 +1808,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.9</v>
+        <v>33.6</v>
       </c>
       <c r="E4" t="n">
-        <v>8.9</v>
+        <v>8.6</v>
       </c>
       <c r="F4" t="n">
         <v>1</v>
@@ -1763,7 +1823,7 @@
         <v>8720</v>
       </c>
       <c r="I4" t="n">
-        <v>773</v>
+        <v>749</v>
       </c>
       <c r="J4" t="n">
         <v>2</v>
@@ -2124,10 +2184,10 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="E13" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="F13" t="n">
         <v>1</v>
@@ -2139,7 +2199,7 @@
         <v>1494</v>
       </c>
       <c r="I13" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2237,65 +2297,65 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>200166011</v>
+        <v>216421567</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>08512</t>
+          <t>00024</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Картридж для Brother HL-L2340DWR</t>
+          <t>Картридж для HP LaserJet 1018</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>32.2</v>
+        <v>34.7</v>
       </c>
       <c r="E16" t="n">
-        <v>7.2</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>2002</v>
+        <v>1513</v>
       </c>
       <c r="I16" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="K16" t="n">
-        <v>2</v>
+        <v>26</v>
       </c>
       <c r="L16" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>199333413</v>
+        <v>200166011</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>08512</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Картридж 50F5H00 для Lexmark MS310d, MS310dn черный</t>
+          <t>Картридж для Brother HL-L2340DWR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>30.8</v>
+        <v>32.2</v>
       </c>
       <c r="E17" t="n">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -2304,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>2383</v>
+        <v>2002</v>
       </c>
       <c r="I17" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L17" t="n">
         <v>7</v>
@@ -2321,23 +2381,23 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>200164027</v>
+        <v>199333413</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>019617</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Картридж для HP PhotoSmart D5060</t>
+          <t>Картридж 50F5H00 для Lexmark MS310d, MS310dn черный</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31.7</v>
+        <v>30.8</v>
       </c>
       <c r="E18" t="n">
-        <v>6.7</v>
+        <v>5.8</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -2346,38 +2406,40 @@
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1884</v>
+        <v>2383</v>
       </c>
       <c r="I18" t="n">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="inlineStr"/>
+        <v>4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>964431688</v>
+        <v>200164027</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>016114</t>
+          <t>019617</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Картридж для Epson Stylus Photo TX710 W</t>
+          <t>Картридж для HP PhotoSmart D5060</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>39.2</v>
+        <v>31.7</v>
       </c>
       <c r="E19" t="n">
-        <v>14.2</v>
+        <v>6.7</v>
       </c>
       <c r="F19" t="n">
         <v>1</v>
@@ -2386,40 +2448,38 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>779</v>
+        <v>1884</v>
       </c>
       <c r="I19" t="n">
-        <v>111</v>
+        <v>127</v>
       </c>
       <c r="J19" t="n">
         <v>1</v>
       </c>
       <c r="K19" t="n">
-        <v>2</v>
-      </c>
-      <c r="L19" t="n">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>263820513</v>
+        <v>964431688</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0595</t>
+          <t>016114</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Картридж LC-1100BK для Brother DCP-145C, DCP-163C черный</t>
+          <t>Картридж для Epson Stylus Photo TX710 W</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>33.1</v>
+        <v>39.4</v>
       </c>
       <c r="E20" t="n">
-        <v>8.1</v>
+        <v>14.4</v>
       </c>
       <c r="F20" t="n">
         <v>1</v>
@@ -2428,162 +2488,164 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>769</v>
+        <v>779</v>
       </c>
       <c r="I20" t="n">
-        <v>62</v>
+        <v>112</v>
       </c>
       <c r="J20" t="n">
         <v>1</v>
       </c>
       <c r="K20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>199566477</v>
+        <v>263820513</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>23654</t>
+          <t>0595</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Картридж для Kyocera EcoSys M2235dn</t>
+          <t>Картридж LC-1100BK для Brother DCP-145C, DCP-163C черный</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29.3</v>
+        <v>33.3</v>
       </c>
       <c r="E21" t="n">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="F21" t="n">
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1401</v>
+        <v>769</v>
       </c>
       <c r="I21" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K21" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>964792524</v>
+        <v>199566477</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>48021</t>
+          <t>23654</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Картридж для P2200</t>
+          <t>Картридж для Kyocera EcoSys M2235dn</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>27.1</v>
+        <v>29.3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1</v>
+        <v>4.3</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>2728</v>
+        <v>1401</v>
       </c>
       <c r="I22" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K22" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L22" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>199574756</v>
+        <v>964792524</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>53511</t>
+          <t>48021</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Картридж для Canon i-SENSYS F-158200</t>
+          <t>Картридж для P2200</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>29</v>
+        <v>27.1</v>
       </c>
       <c r="E23" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>2728</v>
+      </c>
+      <c r="I23" t="n">
+        <v>59</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
         <v>4</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" t="n">
-        <v>1429</v>
-      </c>
-      <c r="I23" t="n">
-        <v>57</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2</v>
-      </c>
-      <c r="K23" t="n">
-        <v>2</v>
       </c>
       <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>967496417</v>
+        <v>199574756</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>53415</t>
+          <t>53511</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Картридж для Samsung ML-2015</t>
+          <t>Картридж для Canon i-SENSYS F-158200</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>27.2</v>
+        <v>29</v>
       </c>
       <c r="E24" t="n">
-        <v>2.2</v>
+        <v>4</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
@@ -2592,40 +2654,38 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>2194</v>
+        <v>1429</v>
       </c>
       <c r="I24" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K24" t="n">
-        <v>3</v>
-      </c>
-      <c r="L24" t="n">
-        <v>24</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>199335608</v>
+        <v>967496417</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5344</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Картридж SCX-4100 для Samsung SCX-4100 черный</t>
+          <t>Картридж для Samsung ML-2015</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>26.4</v>
+        <v>27.2</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -2634,40 +2694,40 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2039</v>
+        <v>2194</v>
       </c>
       <c r="I25" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>199565754</v>
+        <v>199335608</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>08388</t>
+          <t>5344</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Картридж для Epson Expression Home XP-323</t>
+          <t>Картридж SCX-4100 для Samsung SCX-4100 черный</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29.4</v>
+        <v>26.4</v>
       </c>
       <c r="E26" t="n">
-        <v>4.4</v>
+        <v>1.4</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -2676,65 +2736,107 @@
         <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>639</v>
+        <v>2039</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
+        <v>199565754</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>08388</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Картридж для Epson Expression Home XP-323</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="E27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>639</v>
+      </c>
+      <c r="I27" t="n">
+        <v>28</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
         <v>181115802</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2393</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Картридж KP-108in / RP-108 для Canon SELPHY CP1500, CP1300</t>
         </is>
       </c>
-      <c r="D27" t="n">
+      <c r="D28" t="n">
         <v>25.1</v>
       </c>
-      <c r="E27" t="n">
+      <c r="E28" t="n">
         <v>0.1</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
-        <v>0</v>
-      </c>
-      <c r="H27" t="n">
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
         <v>6227</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I28" t="n">
         <v>9</v>
       </c>
-      <c r="J27" t="n">
-        <v>1</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
         <v>7</v>
       </c>
-      <c r="L27" t="n">
+      <c r="L28" t="n">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L27"/>
+  <autoFilter ref="A1:L28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>